--- a/class_excel/stochastic-program.xlsx
+++ b/class_excel/stochastic-program.xlsx
@@ -693,6 +693,17 @@
     <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -705,17 +716,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1135,7 +1135,7 @@
       <c r="S3">
         <v>-10</v>
       </c>
-      <c r="T3" s="33">
+      <c r="T3" s="29">
         <f>SUMPRODUCT($K$2:$S$2,K3:S3)</f>
         <v>-167666.66666666669</v>
       </c>
@@ -2087,8 +2087,8 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="AR6" s="34">
-        <f>SUMPRODUCT(K6:AQ6,$K$5:$AQ$5)</f>
+      <c r="AR6" s="30">
+        <f t="shared" ref="AR6:AR27" si="1">SUMPRODUCT(K6:AQ6,$K$5:$AQ$5)</f>
         <v>-77058.000000000015</v>
       </c>
     </row>
@@ -2150,14 +2150,14 @@
       <c r="AO7" s="6"/>
       <c r="AP7" s="6"/>
       <c r="AQ7" s="7"/>
-      <c r="AR7" s="39">
-        <f>SUMPRODUCT(K7:AQ7,$K$5:$AQ$5)</f>
+      <c r="AR7" s="35">
+        <f t="shared" si="1"/>
         <v>500.00000000000011</v>
       </c>
       <c r="AS7" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="AT7" s="35">
+      <c r="AT7" s="31">
         <v>500</v>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
         <f>D2*E7-D3</f>
         <v>-60</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="40" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -2239,14 +2239,14 @@
       <c r="AO8" s="9"/>
       <c r="AP8" s="9"/>
       <c r="AQ8" s="10"/>
-      <c r="AR8" s="39">
-        <f>SUMPRODUCT(K8:AQ8,$K$5:$AQ$5)</f>
+      <c r="AR8" s="35">
+        <f t="shared" si="1"/>
         <v>199.99999999999994</v>
       </c>
       <c r="AS8" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="AT8" s="36">
+      <c r="AT8" s="32">
         <v>200</v>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="30"/>
+      <c r="I9" s="41"/>
       <c r="J9" t="s">
         <v>3</v>
       </c>
@@ -2307,19 +2307,19 @@
       <c r="AK9" s="12"/>
       <c r="AL9" s="11"/>
       <c r="AQ9" s="12"/>
-      <c r="AR9" s="39">
-        <f>SUMPRODUCT(K9:AQ9,$K$5:$AQ$5)</f>
+      <c r="AR9" s="35">
+        <f t="shared" si="1"/>
         <v>240.00000000000006</v>
       </c>
       <c r="AS9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT9" s="37">
+      <c r="AT9" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I10" s="30"/>
+      <c r="I10" s="41"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
@@ -2360,19 +2360,19 @@
       <c r="AK10" s="12"/>
       <c r="AL10" s="11"/>
       <c r="AQ10" s="12"/>
-      <c r="AR10" s="39">
-        <f>SUMPRODUCT(K10:AQ10,$K$5:$AQ$5)</f>
+      <c r="AR10" s="35">
+        <f t="shared" si="1"/>
         <v>-1.3642420526593924E-12</v>
       </c>
       <c r="AS10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT10" s="37">
+      <c r="AT10" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I11" s="31"/>
+      <c r="I11" s="42"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
       </c>
@@ -2427,19 +2427,19 @@
       <c r="AO11" s="14"/>
       <c r="AP11" s="14"/>
       <c r="AQ11" s="15"/>
-      <c r="AR11" s="39">
-        <f>SUMPRODUCT(K11:AQ11,$K$5:$AQ$5)</f>
+      <c r="AR11" s="35">
+        <f t="shared" si="1"/>
         <v>-6000</v>
       </c>
       <c r="AS11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT11" s="37">
+      <c r="AT11" s="33">
         <v>-6000</v>
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="43" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -2496,19 +2496,19 @@
       <c r="AO12" s="9"/>
       <c r="AP12" s="9"/>
       <c r="AQ12" s="10"/>
-      <c r="AR12" s="39">
-        <f>SUMPRODUCT(K12:AQ12,$K$5:$AQ$5)</f>
+      <c r="AR12" s="35">
+        <f t="shared" si="1"/>
         <v>200.00000000000006</v>
       </c>
       <c r="AS12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="AT12" s="35">
+      <c r="AT12" s="31">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I13" s="30"/>
+      <c r="I13" s="41"/>
       <c r="J13" t="s">
         <v>3</v>
       </c>
@@ -2547,19 +2547,19 @@
       <c r="AK13" s="12"/>
       <c r="AL13" s="11"/>
       <c r="AQ13" s="12"/>
-      <c r="AR13" s="39">
-        <f>SUMPRODUCT(K13:AQ13,$K$5:$AQ$5)</f>
+      <c r="AR13" s="35">
+        <f t="shared" si="1"/>
         <v>240.00000000000006</v>
       </c>
       <c r="AS13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT13" s="37">
+      <c r="AT13" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I14" s="30"/>
+      <c r="I14" s="41"/>
       <c r="J14" t="s">
         <v>27</v>
       </c>
@@ -2598,19 +2598,19 @@
       <c r="AK14" s="12"/>
       <c r="AL14" s="11"/>
       <c r="AQ14" s="12"/>
-      <c r="AR14" s="39">
-        <f>SUMPRODUCT(K14:AQ14,$K$5:$AQ$5)</f>
+      <c r="AR14" s="35">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AS14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT14" s="37">
+      <c r="AT14" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I15" s="31"/>
+      <c r="I15" s="42"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
       </c>
@@ -2665,19 +2665,19 @@
       <c r="AO15" s="14"/>
       <c r="AP15" s="14"/>
       <c r="AQ15" s="15"/>
-      <c r="AR15" s="39">
-        <f>SUMPRODUCT(K15:AQ15,$K$5:$AQ$5)</f>
+      <c r="AR15" s="35">
+        <f t="shared" si="1"/>
         <v>-6000</v>
       </c>
       <c r="AS15" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AT15" s="38">
+      <c r="AT15" s="34">
         <v>-6000</v>
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.35">
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="43" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -2735,19 +2735,19 @@
       <c r="AO16" s="9"/>
       <c r="AP16" s="9"/>
       <c r="AQ16" s="10"/>
-      <c r="AR16" s="39">
-        <f>SUMPRODUCT(K16:AQ16,$K$5:$AQ$5)</f>
+      <c r="AR16" s="35">
+        <f t="shared" si="1"/>
         <v>200</v>
       </c>
       <c r="AS16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT16" s="37">
+      <c r="AT16" s="33">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I17" s="30"/>
+      <c r="I17" s="41"/>
       <c r="J17" t="s">
         <v>3</v>
       </c>
@@ -2787,19 +2787,19 @@
       <c r="AK17" s="12"/>
       <c r="AL17" s="11"/>
       <c r="AQ17" s="12"/>
-      <c r="AR17" s="39">
-        <f>SUMPRODUCT(K17:AQ17,$K$5:$AQ$5)</f>
+      <c r="AR17" s="35">
+        <f t="shared" si="1"/>
         <v>240.00000000000006</v>
       </c>
       <c r="AS17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT17" s="37">
+      <c r="AT17" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="18" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I18" s="30"/>
+      <c r="I18" s="41"/>
       <c r="J18" t="s">
         <v>27</v>
       </c>
@@ -2839,19 +2839,19 @@
       <c r="AK18" s="12"/>
       <c r="AL18" s="11"/>
       <c r="AQ18" s="12"/>
-      <c r="AR18" s="39">
-        <f>SUMPRODUCT(K18:AQ18,$K$5:$AQ$5)</f>
+      <c r="AR18" s="35">
+        <f t="shared" si="1"/>
         <v>-9.0949470177292824E-13</v>
       </c>
       <c r="AS18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT18" s="37">
+      <c r="AT18" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I19" s="31"/>
+      <c r="I19" s="42"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
       </c>
@@ -2903,19 +2903,19 @@
       <c r="AO19" s="14"/>
       <c r="AP19" s="14"/>
       <c r="AQ19" s="15"/>
-      <c r="AR19" s="39">
-        <f>SUMPRODUCT(K19:AQ19,$K$5:$AQ$5)</f>
+      <c r="AR19" s="35">
+        <f t="shared" si="1"/>
         <v>-4800.0000000000009</v>
       </c>
       <c r="AS19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AT19" s="38">
+      <c r="AT19" s="34">
         <v>-6000</v>
       </c>
     </row>
     <row r="20" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I20" s="32"/>
+      <c r="I20" s="43"/>
       <c r="J20" s="9" t="s">
         <v>2</v>
       </c>
@@ -2970,19 +2970,19 @@
       <c r="AO20" s="9"/>
       <c r="AP20" s="9"/>
       <c r="AQ20" s="10"/>
-      <c r="AR20" s="39">
-        <f>SUMPRODUCT(K20:AQ20,$K$5:$AQ$5)</f>
+      <c r="AR20" s="35">
+        <f t="shared" si="1"/>
         <v>200.00000000000006</v>
       </c>
       <c r="AS20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT20" s="37">
+      <c r="AT20" s="33">
         <v>200</v>
       </c>
     </row>
     <row r="21" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I21" s="30"/>
+      <c r="I21" s="41"/>
       <c r="J21" t="s">
         <v>3</v>
       </c>
@@ -3021,19 +3021,19 @@
       </c>
       <c r="AL21" s="11"/>
       <c r="AQ21" s="12"/>
-      <c r="AR21" s="39">
-        <f>SUMPRODUCT(K21:AQ21,$K$5:$AQ$5)</f>
+      <c r="AR21" s="35">
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="AS21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT21" s="37">
+      <c r="AT21" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="22" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I22" s="30"/>
+      <c r="I22" s="41"/>
       <c r="J22" t="s">
         <v>27</v>
       </c>
@@ -3072,19 +3072,19 @@
       </c>
       <c r="AL22" s="11"/>
       <c r="AQ22" s="12"/>
-      <c r="AR22" s="39">
-        <f>SUMPRODUCT(K22:AQ22,$K$5:$AQ$5)</f>
+      <c r="AR22" s="35">
+        <f t="shared" si="1"/>
         <v>-9.0949470177292824E-13</v>
       </c>
       <c r="AS22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT22" s="37">
+      <c r="AT22" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I23" s="31"/>
+      <c r="I23" s="42"/>
       <c r="J23" s="14" t="s">
         <v>28</v>
       </c>
@@ -3136,19 +3136,19 @@
       <c r="AO23" s="14"/>
       <c r="AP23" s="14"/>
       <c r="AQ23" s="15"/>
-      <c r="AR23" s="39">
-        <f>SUMPRODUCT(K23:AQ23,$K$5:$AQ$5)</f>
+      <c r="AR23" s="35">
+        <f t="shared" si="1"/>
         <v>-3600.0000000000009</v>
       </c>
       <c r="AS23" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AT23" s="38">
+      <c r="AT23" s="34">
         <v>-6000</v>
       </c>
     </row>
     <row r="24" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I24" s="32"/>
+      <c r="I24" s="43"/>
       <c r="J24" s="9" t="s">
         <v>2</v>
       </c>
@@ -3203,19 +3203,19 @@
       <c r="AQ24" s="10">
         <v>0</v>
       </c>
-      <c r="AR24" s="39">
-        <f>SUMPRODUCT(K24:AQ24,$K$5:$AQ$5)</f>
+      <c r="AR24" s="35">
+        <f t="shared" si="1"/>
         <v>200.00000000000009</v>
       </c>
       <c r="AS24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT24" s="37">
+      <c r="AT24" s="33">
         <v>200</v>
       </c>
     </row>
     <row r="25" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I25" s="30"/>
+      <c r="I25" s="41"/>
       <c r="J25" t="s">
         <v>3</v>
       </c>
@@ -3254,19 +3254,19 @@
       <c r="AQ25" s="12">
         <v>0</v>
       </c>
-      <c r="AR25" s="39">
-        <f>SUMPRODUCT(K25:AQ25,$K$5:$AQ$5)</f>
+      <c r="AR25" s="35">
+        <f t="shared" si="1"/>
         <v>240.00000000000017</v>
       </c>
       <c r="AS25" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT25" s="37">
+      <c r="AT25" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="26" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I26" s="30"/>
+      <c r="I26" s="41"/>
       <c r="J26" t="s">
         <v>27</v>
       </c>
@@ -3305,19 +3305,19 @@
       <c r="AQ26" s="12">
         <v>-1</v>
       </c>
-      <c r="AR26" s="39">
-        <f>SUMPRODUCT(K26:AQ26,$K$5:$AQ$5)</f>
+      <c r="AR26" s="35">
+        <f t="shared" si="1"/>
         <v>-1.3642420526593924E-12</v>
       </c>
       <c r="AS26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AT26" s="37">
+      <c r="AT26" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="9:46" x14ac:dyDescent="0.35">
-      <c r="I27" s="31"/>
+      <c r="I27" s="42"/>
       <c r="J27" s="14" t="s">
         <v>28</v>
       </c>
@@ -3369,14 +3369,14 @@
       <c r="AQ27" s="15">
         <v>0</v>
       </c>
-      <c r="AR27" s="39">
-        <f>SUMPRODUCT(K27:AQ27,$K$5:$AQ$5)</f>
+      <c r="AR27" s="35">
+        <f t="shared" si="1"/>
         <v>-6000</v>
       </c>
       <c r="AS27" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AT27" s="38">
+      <c r="AT27" s="34">
         <v>-6000</v>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
         <f t="shared" si="1"/>
         <v>-3.333333333333333</v>
       </c>
-      <c r="AF6" s="34">
+      <c r="AF6" s="30">
         <f>SUMPRODUCT(K6:AE6,$K$5:$AE$5)</f>
         <v>-108389.99999999997</v>
       </c>
@@ -3900,14 +3900,14 @@
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
       <c r="AE7" s="7"/>
-      <c r="AF7" s="39">
+      <c r="AF7" s="35">
         <f t="shared" ref="AF7:AF19" si="2">SUMPRODUCT(K7:AE7,$K$5:$AE$5)</f>
         <v>499.99999999999994</v>
       </c>
       <c r="AG7" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="AH7" s="35">
+      <c r="AH7" s="31">
         <v>500</v>
       </c>
     </row>
@@ -3931,7 +3931,7 @@
         <f>D2*E7-D3</f>
         <v>-60</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="40" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -3977,14 +3977,14 @@
       <c r="AC8" s="9"/>
       <c r="AD8" s="9"/>
       <c r="AE8" s="10"/>
-      <c r="AF8" s="40">
+      <c r="AF8" s="36">
         <f t="shared" si="2"/>
         <v>199.99999999999989</v>
       </c>
       <c r="AG8" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="AH8" s="36">
+      <c r="AH8" s="32">
         <v>200</v>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="30"/>
+      <c r="I9" s="41"/>
       <c r="J9" t="s">
         <v>3</v>
       </c>
@@ -4041,19 +4041,19 @@
       <c r="Y9" s="12"/>
       <c r="Z9" s="11"/>
       <c r="AE9" s="12"/>
-      <c r="AF9" s="41">
+      <c r="AF9" s="37">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="AG9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH9" s="37">
+      <c r="AH9" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I10" s="30"/>
+      <c r="I10" s="41"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
@@ -4090,19 +4090,19 @@
       <c r="Y10" s="12"/>
       <c r="Z10" s="11"/>
       <c r="AE10" s="12"/>
-      <c r="AF10" s="42">
+      <c r="AF10" s="38">
         <f t="shared" si="2"/>
         <v>-9.0949470177292824E-13</v>
       </c>
       <c r="AG10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH10" s="37">
+      <c r="AH10" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I11" s="31"/>
+      <c r="I11" s="42"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
       </c>
@@ -4145,19 +4145,19 @@
       <c r="AC11" s="14"/>
       <c r="AD11" s="14"/>
       <c r="AE11" s="15"/>
-      <c r="AF11" s="41">
+      <c r="AF11" s="37">
         <f t="shared" si="2"/>
         <v>-5999.9999999999991</v>
       </c>
       <c r="AG11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH11" s="37">
+      <c r="AH11" s="33">
         <v>-6000</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="43" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -4202,19 +4202,19 @@
       <c r="AC12" s="9"/>
       <c r="AD12" s="9"/>
       <c r="AE12" s="10"/>
-      <c r="AF12" s="43">
+      <c r="AF12" s="39">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="AG12" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="AH12" s="35">
+      <c r="AH12" s="31">
         <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I13" s="30"/>
+      <c r="I13" s="41"/>
       <c r="J13" t="s">
         <v>3</v>
       </c>
@@ -4249,19 +4249,19 @@
       </c>
       <c r="Z13" s="11"/>
       <c r="AE13" s="12"/>
-      <c r="AF13" s="41">
+      <c r="AF13" s="37">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="AG13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH13" s="37">
+      <c r="AH13" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I14" s="30"/>
+      <c r="I14" s="41"/>
       <c r="J14" t="s">
         <v>27</v>
       </c>
@@ -4296,19 +4296,19 @@
       </c>
       <c r="Z14" s="11"/>
       <c r="AE14" s="12"/>
-      <c r="AF14" s="41">
+      <c r="AF14" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH14" s="37">
+      <c r="AH14" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I15" s="31"/>
+      <c r="I15" s="42"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
       </c>
@@ -4351,19 +4351,19 @@
       <c r="AC15" s="14"/>
       <c r="AD15" s="14"/>
       <c r="AE15" s="15"/>
-      <c r="AF15" s="39">
+      <c r="AF15" s="35">
         <f t="shared" si="2"/>
         <v>-4999.9999999999991</v>
       </c>
       <c r="AG15" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AH15" s="38">
+      <c r="AH15" s="34">
         <v>-6000</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="43" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -4409,19 +4409,19 @@
       <c r="AE16" s="10">
         <v>0</v>
       </c>
-      <c r="AF16" s="41">
+      <c r="AF16" s="37">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="AG16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH16" s="37">
+      <c r="AH16" s="33">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I17" s="30"/>
+      <c r="I17" s="41"/>
       <c r="J17" t="s">
         <v>3</v>
       </c>
@@ -4457,19 +4457,19 @@
       <c r="AE17" s="12">
         <v>0</v>
       </c>
-      <c r="AF17" s="41">
+      <c r="AF17" s="37">
         <f t="shared" si="2"/>
         <v>240</v>
       </c>
       <c r="AG17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH17" s="37">
+      <c r="AH17" s="33">
         <v>240</v>
       </c>
     </row>
     <row r="18" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I18" s="30"/>
+      <c r="I18" s="41"/>
       <c r="J18" t="s">
         <v>27</v>
       </c>
@@ -4505,19 +4505,19 @@
       <c r="AE18" s="12">
         <v>-1</v>
       </c>
-      <c r="AF18" s="41">
+      <c r="AF18" s="37">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AG18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AH18" s="37">
+      <c r="AH18" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="9:34" x14ac:dyDescent="0.35">
-      <c r="I19" s="31"/>
+      <c r="I19" s="42"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
       </c>
@@ -4560,14 +4560,14 @@
       <c r="AE19" s="15">
         <v>0</v>
       </c>
-      <c r="AF19" s="39">
+      <c r="AF19" s="35">
         <f t="shared" si="2"/>
         <v>-3999.9999999999991</v>
       </c>
       <c r="AG19" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="AH19" s="38">
+      <c r="AH19" s="34">
         <v>-6000</v>
       </c>
     </row>
@@ -4951,21 +4951,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005D21A9346877C94FBE0D2EF98A54C8DF" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b9d30dfdbb3c728c42ac273b0b267a13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0f411969-aaa6-47b2-a14e-e9510c0df77f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ca649492ee4635bde6ac1a281be3e98b" ns2:_="">
     <xsd:import namespace="0f411969-aaa6-47b2-a14e-e9510c0df77f"/>
@@ -5103,24 +5088,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{348553ED-7DD9-4264-9A54-B9B6A7F9271D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF2361-3021-4691-B065-35782F57E24B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA817907-0C0B-4F48-8DFB-81DCD08F0DDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5136,4 +5119,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF2361-3021-4691-B065-35782F57E24B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{348553ED-7DD9-4264-9A54-B9B6A7F9271D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/class_excel/stochastic-program.xlsx
+++ b/class_excel/stochastic-program.xlsx
@@ -1,155 +1,198 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451DC630-1795-43E8-AF32-1FCBC917EBBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C6C9AF-3B9F-42DF-90F6-64E27FC42CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="805" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="805" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="farmer0" sheetId="6" r:id="rId1"/>
-    <sheet name="farmerSP (2)" sheetId="20" r:id="rId2"/>
-    <sheet name="farmerSP" sheetId="9" r:id="rId3"/>
-    <sheet name="2prod" sheetId="19" r:id="rId4"/>
+    <sheet name="farmerSP (3)" sheetId="21" r:id="rId2"/>
+    <sheet name="farmerSP (2)" sheetId="20" r:id="rId3"/>
+    <sheet name="farmerSP" sheetId="9" r:id="rId4"/>
+    <sheet name="2prod" sheetId="19" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">farmer0!$K$2:$S$2</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">farmerSP!$K$5:$AE$5</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">'farmerSP (2)'!$K$5:$AQ$5</definedName>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">farmerSP!$K$5:$AE$5</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'farmerSP (2)'!$K$5:$AQ$5</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'farmerSP (3)'!$I$5:$AC$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">farmer0!$T$4</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">farmerSP!$AF$7</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">farmerSP!$AF$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$7</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">farmer0!$T$5:$T$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">farmerSP!$AF$8:$AF$19</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$8:$AR$27</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">farmerSP!$AF$8:$AF$19</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$8:$AR$27</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$8:$AD$19</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">farmer0!$T$5:$T$8</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_lhs4" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs4" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs4" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_lhs5" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs5" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs5" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="3" hidden="1">'2prod'!$O$10</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">'2prod'!$O$10</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">farmer0!$T$3</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">farmerSP!$AF$6</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$6</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">farmerSP!$AF$6</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$6</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$6</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rel4" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rel4" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rel5" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">farmer0!$V$4</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">farmerSP!$AH$7</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'farmerSP (2)'!$AT$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">farmerSP!$AH$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'farmerSP (2)'!$AT$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'farmerSP (3)'!$AF$7</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">farmer0!$V$5:$V$8</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">farmerSP!$AH$8:$AH$19</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'farmerSP (2)'!$AT$8:$AT$27</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">farmerSP!$AH$8:$AH$19</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'farmerSP (2)'!$AT$8:$AT$27</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'farmerSP (3)'!$AF$8:$AF$19</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">farmer0!$V$5:$V$8</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_rhs4" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs4" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs4" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_rhs5" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs5" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs5" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
@@ -165,8 +208,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -174,7 +215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="74">
   <si>
     <t>=</t>
   </si>
@@ -404,21 +445,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="187" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="188" formatCode="0.00000"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -429,12 +470,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,6 +503,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -650,10 +697,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="187" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -661,7 +708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -690,7 +737,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -716,6 +763,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -999,18 +1052,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CD3D5A0-F96E-4065-ADE4-1E546597877D}">
   <dimension ref="A1:V9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.9375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.8125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1048,7 +1101,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1092,7 +1145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1140,7 +1193,7 @@
         <v>-167666.66666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1194,7 +1247,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1249,7 +1302,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -1298,7 +1351,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1356,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1417,7 +1470,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1440,40 +1493,1260 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56BFB45-A76E-4970-AED8-74E019095023}">
+  <dimension ref="A1:AF19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="11" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="3.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="44"/>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1">
+        <v>150</v>
+      </c>
+      <c r="J1">
+        <v>230</v>
+      </c>
+      <c r="K1">
+        <v>260</v>
+      </c>
+      <c r="L1">
+        <v>238</v>
+      </c>
+      <c r="M1">
+        <v>210</v>
+      </c>
+      <c r="N1">
+        <v>-170</v>
+      </c>
+      <c r="O1">
+        <v>-150</v>
+      </c>
+      <c r="P1">
+        <v>-36</v>
+      </c>
+      <c r="Q1">
+        <v>-10</v>
+      </c>
+      <c r="R1">
+        <v>238</v>
+      </c>
+      <c r="S1">
+        <v>210</v>
+      </c>
+      <c r="T1">
+        <v>-170</v>
+      </c>
+      <c r="U1">
+        <v>-150</v>
+      </c>
+      <c r="V1">
+        <v>-36</v>
+      </c>
+      <c r="W1">
+        <v>-10</v>
+      </c>
+      <c r="X1">
+        <v>238</v>
+      </c>
+      <c r="Y1">
+        <v>210</v>
+      </c>
+      <c r="Z1">
+        <v>-170</v>
+      </c>
+      <c r="AA1">
+        <v>-150</v>
+      </c>
+      <c r="AB1">
+        <v>-36</v>
+      </c>
+      <c r="AC1">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2.5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="F2" s="44"/>
+      <c r="H2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:AC2" si="0">1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" si="0"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>150</v>
+      </c>
+      <c r="C3">
+        <v>230</v>
+      </c>
+      <c r="D3">
+        <v>260</v>
+      </c>
+      <c r="F3" s="44"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>200</v>
+      </c>
+      <c r="C4">
+        <v>240</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="44"/>
+      <c r="I4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="W4" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="X4" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="46" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA4" s="46" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB4" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="AC4" s="46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>238</v>
+      </c>
+      <c r="C5">
+        <v>210</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="44"/>
+      <c r="H5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="27">
+        <v>10</v>
+      </c>
+      <c r="J5" s="27">
+        <v>10</v>
+      </c>
+      <c r="K5" s="27">
+        <v>10</v>
+      </c>
+      <c r="L5" s="27">
+        <v>10</v>
+      </c>
+      <c r="M5" s="27">
+        <v>10</v>
+      </c>
+      <c r="N5" s="27">
+        <v>10</v>
+      </c>
+      <c r="O5" s="27">
+        <v>10</v>
+      </c>
+      <c r="P5" s="27">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="27">
+        <v>10</v>
+      </c>
+      <c r="R5" s="27">
+        <v>10</v>
+      </c>
+      <c r="S5" s="27">
+        <v>10</v>
+      </c>
+      <c r="T5" s="27">
+        <v>10</v>
+      </c>
+      <c r="U5" s="27">
+        <v>10</v>
+      </c>
+      <c r="V5" s="27">
+        <v>10</v>
+      </c>
+      <c r="W5" s="27">
+        <v>10</v>
+      </c>
+      <c r="X5" s="47">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="47">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="47">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="47">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="47">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="44"/>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="8">
+        <f>I1*I2</f>
+        <v>150</v>
+      </c>
+      <c r="J6" s="9">
+        <f t="shared" ref="J6:AC6" si="1">J1*J2</f>
+        <v>230</v>
+      </c>
+      <c r="K6" s="9">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="L6" s="8">
+        <f>L1*L2</f>
+        <v>79.333333333333329</v>
+      </c>
+      <c r="M6" s="9">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="N6" s="9">
+        <f t="shared" si="1"/>
+        <v>-56.666666666666664</v>
+      </c>
+      <c r="O6" s="9">
+        <f t="shared" si="1"/>
+        <v>-50</v>
+      </c>
+      <c r="P6" s="9">
+        <f t="shared" si="1"/>
+        <v>-12</v>
+      </c>
+      <c r="Q6" s="10">
+        <f t="shared" si="1"/>
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="R6" s="8">
+        <f t="shared" si="1"/>
+        <v>79.333333333333329</v>
+      </c>
+      <c r="S6" s="9">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="T6" s="9">
+        <f t="shared" si="1"/>
+        <v>-56.666666666666664</v>
+      </c>
+      <c r="U6" s="9">
+        <f t="shared" si="1"/>
+        <v>-50</v>
+      </c>
+      <c r="V6" s="9">
+        <f t="shared" si="1"/>
+        <v>-12</v>
+      </c>
+      <c r="W6" s="10">
+        <f t="shared" si="1"/>
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="X6" s="19">
+        <f t="shared" si="1"/>
+        <v>79.333333333333329</v>
+      </c>
+      <c r="Y6" s="19">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="Z6" s="19">
+        <f t="shared" si="1"/>
+        <v>-56.666666666666664</v>
+      </c>
+      <c r="AA6" s="19">
+        <f t="shared" si="1"/>
+        <v>-50</v>
+      </c>
+      <c r="AB6" s="19">
+        <f t="shared" si="1"/>
+        <v>-12</v>
+      </c>
+      <c r="AC6" s="19">
+        <f t="shared" si="1"/>
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AD6" s="30">
+        <f>SUMPRODUCT(I6:AC6,$I$5:$AC$5)</f>
+        <v>7220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>170</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7">
+        <v>36</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="44"/>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="35">
+        <f>SUMPRODUCT(I7:AC7,$I$5:$AC$5)</f>
+        <v>30</v>
+      </c>
+      <c r="AE7" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="31">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <f>B2*B7-B3</f>
+        <v>275</v>
+      </c>
+      <c r="C8">
+        <f>C2*C7-C3</f>
+        <v>220</v>
+      </c>
+      <c r="D8">
+        <f>D2*D7-D3</f>
+        <v>460</v>
+      </c>
+      <c r="E8">
+        <f>D2*E7-D3</f>
+        <v>-60</v>
+      </c>
+      <c r="F8" s="44"/>
+      <c r="G8" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" s="8">
+        <f>1.2*2.5</f>
+        <v>3</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="10"/>
+      <c r="AD8" s="35">
+        <f>SUMPRODUCT(I8:AC8,$I$5:$AC$5)</f>
+        <v>30</v>
+      </c>
+      <c r="AE8" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF8" s="32">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="44"/>
+      <c r="G9" s="41"/>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="11">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>1.2*3</f>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>-1</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="12">
+        <v>0</v>
+      </c>
+      <c r="R9" s="11"/>
+      <c r="S9" s="4"/>
+      <c r="W9" s="12"/>
+      <c r="X9" s="11"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="35">
+        <f>SUMPRODUCT(I9:AC9,$I$5:$AC$5)</f>
+        <v>36</v>
+      </c>
+      <c r="AE9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF9" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F10" s="44"/>
+      <c r="G10" s="41"/>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="11">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="12">
+        <f>1.2*20</f>
+        <v>24</v>
+      </c>
+      <c r="L10" s="11">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-1</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>-1</v>
+      </c>
+      <c r="R10" s="11"/>
+      <c r="S10" s="4"/>
+      <c r="W10" s="12"/>
+      <c r="X10" s="11"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="35">
+        <f>SUMPRODUCT(I10:AC10,$I$5:$AC$5)</f>
+        <v>220</v>
+      </c>
+      <c r="AE10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF10" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F11" s="44"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="15">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
+        <v>0</v>
+      </c>
+      <c r="O11" s="14">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>-1</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13"/>
+      <c r="S11" s="14"/>
+      <c r="T11" s="14"/>
+      <c r="U11" s="14"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="14"/>
+      <c r="Z11" s="14"/>
+      <c r="AA11" s="14"/>
+      <c r="AB11" s="14"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="35">
+        <f>SUMPRODUCT(I11:AC11,$I$5:$AC$5)</f>
+        <v>-10</v>
+      </c>
+      <c r="AE11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF11" s="33">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F12" s="44"/>
+      <c r="G12" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I12" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="8">
+        <v>1</v>
+      </c>
+      <c r="S12" s="9">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9">
+        <v>-1</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="10">
+        <v>0</v>
+      </c>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9"/>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="10"/>
+      <c r="AD12" s="35">
+        <f>SUMPRODUCT(I12:AC12,$I$5:$AC$5)</f>
+        <v>25</v>
+      </c>
+      <c r="AE12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF12" s="31">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F13" s="44"/>
+      <c r="G13" s="41"/>
+      <c r="H13" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+      <c r="L13" s="11"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="11">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>-1</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13" s="12">
+        <v>0</v>
+      </c>
+      <c r="X13" s="11"/>
+      <c r="AC13" s="12"/>
+      <c r="AD13" s="35">
+        <f>SUMPRODUCT(I13:AC13,$I$5:$AC$5)</f>
+        <v>30</v>
+      </c>
+      <c r="AE13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF13" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F14" s="44"/>
+      <c r="G14" s="41"/>
+      <c r="H14" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="12">
+        <v>20</v>
+      </c>
+      <c r="L14" s="11"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="11">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>-1</v>
+      </c>
+      <c r="W14" s="12">
+        <v>-1</v>
+      </c>
+      <c r="X14" s="11"/>
+      <c r="AC14" s="12"/>
+      <c r="AD14" s="35">
+        <f>SUMPRODUCT(I14:AC14,$I$5:$AC$5)</f>
+        <v>180</v>
+      </c>
+      <c r="AE14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF14" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F15" s="44"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="13">
+        <v>0</v>
+      </c>
+      <c r="S15" s="14">
+        <v>0</v>
+      </c>
+      <c r="T15" s="14">
+        <v>0</v>
+      </c>
+      <c r="U15" s="14">
+        <v>0</v>
+      </c>
+      <c r="V15" s="14">
+        <v>-1</v>
+      </c>
+      <c r="W15" s="15">
+        <v>0</v>
+      </c>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="14"/>
+      <c r="Z15" s="14"/>
+      <c r="AA15" s="14"/>
+      <c r="AB15" s="14"/>
+      <c r="AC15" s="15"/>
+      <c r="AD15" s="35">
+        <f>SUMPRODUCT(I15:AC15,$I$5:$AC$5)</f>
+        <v>-10</v>
+      </c>
+      <c r="AE15" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF15" s="34">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="F16" s="44"/>
+      <c r="G16" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="8">
+        <f>0.8*2.5</f>
+        <v>2</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>-1</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="35">
+        <f>SUMPRODUCT(I16:AC16,$I$5:$AC$5)</f>
+        <v>20</v>
+      </c>
+      <c r="AE16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF16" s="33">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="6:32" x14ac:dyDescent="0.25">
+      <c r="F17" s="44"/>
+      <c r="G17" s="41"/>
+      <c r="H17" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0</v>
+      </c>
+      <c r="J17" s="45">
+        <f>0.8*3</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="11"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>-1</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="12">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="35">
+        <f>SUMPRODUCT(I17:AC17,$I$5:$AC$5)</f>
+        <v>24</v>
+      </c>
+      <c r="AE17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF17" s="33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="6:32" x14ac:dyDescent="0.25">
+      <c r="F18" s="44"/>
+      <c r="G18" s="41"/>
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0</v>
+      </c>
+      <c r="J18" s="45">
+        <v>0</v>
+      </c>
+      <c r="K18" s="12">
+        <f>0.8*20</f>
+        <v>16</v>
+      </c>
+      <c r="L18" s="11"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="11"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>-1</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>-1</v>
+      </c>
+      <c r="AD18" s="35">
+        <f>SUMPRODUCT(I18:AC18,$I$5:$AC$5)</f>
+        <v>140</v>
+      </c>
+      <c r="AE18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF18" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="6:32" x14ac:dyDescent="0.25">
+      <c r="F19" s="44"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14">
+        <v>0</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="14">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="14">
+        <v>-1</v>
+      </c>
+      <c r="AC19" s="15">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="35">
+        <f>SUMPRODUCT(I19:AC19,$I$5:$AC$5)</f>
+        <v>-10</v>
+      </c>
+      <c r="AE19" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF19" s="34">
+        <v>-6000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="G12:G15"/>
+    <mergeCell ref="G16:G19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25CF1EED-2747-49F4-88EF-A266F263C174}">
   <dimension ref="A1:AT27"/>
-  <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.9375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.0625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.4375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.1875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.1875" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="5.4375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="4.6875" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="4.4375" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="4.6875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="3.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
@@ -1586,7 +2859,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="2" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1702,7 +2975,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1716,7 +2989,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1829,7 +3102,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1945,7 +3218,7 @@
         <v>1380.0000000000014</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -2092,7 +3365,7 @@
         <v>-77058.000000000015</v>
       </c>
     </row>
-    <row r="7" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2161,7 +3434,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2250,7 +3523,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2318,7 +3591,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I10" s="41"/>
       <c r="J10" t="s">
         <v>27</v>
@@ -2371,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I11" s="42"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
@@ -2438,7 +3711,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I12" s="43" t="s">
         <v>49</v>
       </c>
@@ -2507,7 +3780,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I13" s="41"/>
       <c r="J13" t="s">
         <v>3</v>
@@ -2558,7 +3831,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I14" s="41"/>
       <c r="J14" t="s">
         <v>27</v>
@@ -2609,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I15" s="42"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
@@ -2676,7 +3949,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="16" spans="1:46" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="I16" s="43" t="s">
         <v>52</v>
       </c>
@@ -2746,7 +4019,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="17" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I17" s="41"/>
       <c r="J17" t="s">
         <v>3</v>
@@ -2798,7 +4071,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="18" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I18" s="41"/>
       <c r="J18" t="s">
         <v>27</v>
@@ -2850,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="19" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I19" s="42"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
@@ -2914,7 +4187,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="20" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="20" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I20" s="43"/>
       <c r="J20" s="9" t="s">
         <v>2</v>
@@ -2981,7 +4254,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="21" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I21" s="41"/>
       <c r="J21" t="s">
         <v>3</v>
@@ -3032,7 +4305,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="22" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I22" s="41"/>
       <c r="J22" t="s">
         <v>27</v>
@@ -3083,7 +4356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="23" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I23" s="42"/>
       <c r="J23" s="14" t="s">
         <v>28</v>
@@ -3147,7 +4420,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="24" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="24" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I24" s="43"/>
       <c r="J24" s="9" t="s">
         <v>2</v>
@@ -3214,7 +4487,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="25" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I25" s="41"/>
       <c r="J25" t="s">
         <v>3</v>
@@ -3265,7 +4538,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="26" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="26" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I26" s="41"/>
       <c r="J26" t="s">
         <v>27</v>
@@ -3316,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="9:46" x14ac:dyDescent="0.35">
+    <row r="27" spans="9:46" x14ac:dyDescent="0.25">
       <c r="I27" s="42"/>
       <c r="J27" s="14" t="s">
         <v>28</v>
@@ -3393,23 +4666,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37E63B8-EB9D-4227-BEBC-562734DDEEDE}">
   <dimension ref="A1:AH19"/>
-  <sheetFormatPr defaultColWidth="8.9375" defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.9375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.0625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1875" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.5625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.5703125" customWidth="1"/>
     <col min="14" max="31" width="5" customWidth="1"/>
     <col min="33" max="33" width="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
@@ -3486,7 +4759,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3584,7 +4857,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3598,7 +4871,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3675,7 +4948,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -3755,7 +5028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="13.9" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>6</v>
       </c>
@@ -3854,7 +5127,7 @@
         <v>-108389.99999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3911,7 +5184,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3988,7 +5261,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -4052,7 +5325,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I10" s="41"/>
       <c r="J10" t="s">
         <v>27</v>
@@ -4101,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I11" s="42"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
@@ -4156,7 +5429,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I12" s="43" t="s">
         <v>49</v>
       </c>
@@ -4213,7 +5486,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I13" s="41"/>
       <c r="J13" t="s">
         <v>3</v>
@@ -4260,7 +5533,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I14" s="41"/>
       <c r="J14" t="s">
         <v>27</v>
@@ -4307,7 +5580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I15" s="42"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
@@ -4362,7 +5635,7 @@
         <v>-6000</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="I16" s="43" t="s">
         <v>52</v>
       </c>
@@ -4420,7 +5693,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="9:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="9:34" x14ac:dyDescent="0.25">
       <c r="I17" s="41"/>
       <c r="J17" t="s">
         <v>3</v>
@@ -4468,7 +5741,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="9:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="9:34" x14ac:dyDescent="0.25">
       <c r="I18" s="41"/>
       <c r="J18" t="s">
         <v>27</v>
@@ -4516,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="9:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="9:34" x14ac:dyDescent="0.25">
       <c r="I19" s="42"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
@@ -4581,19 +5854,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E936C5E6-48EB-470A-826D-E40B341C7C76}">
   <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.9375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.5625" customWidth="1"/>
-    <col min="8" max="8" width="7.8125" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -4619,7 +5892,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4648,7 +5921,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4677,7 +5950,7 @@
         <v>0.34</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4706,7 +5979,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4736,7 +6009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4759,7 +6032,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4783,7 +6056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4800,7 +6073,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4817,7 +6090,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4834,7 +6107,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4851,7 +6124,7 @@
         <v>0.10200000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4868,7 +6141,7 @@
         <v>1.6500000000000001E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4885,7 +6158,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4902,7 +6175,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4919,7 +6192,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4936,7 +6209,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -5089,18 +6362,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5122,18 +6395,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF2361-3021-4691-B065-35782F57E24B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{348553ED-7DD9-4264-9A54-B9B6A7F9271D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBF2361-3021-4691-B065-35782F57E24B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/class_excel/stochastic-program.xlsx
+++ b/class_excel/stochastic-program.xlsx
@@ -1,198 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\class_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\class_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C6C9AF-3B9F-42DF-90F6-64E27FC42CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CD34DB-5273-420C-BCFD-FA6EF69DD86D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="805" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="805" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="farmer0" sheetId="6" r:id="rId1"/>
-    <sheet name="farmerSP (3)" sheetId="21" r:id="rId2"/>
-    <sheet name="farmerSP (2)" sheetId="20" r:id="rId3"/>
-    <sheet name="farmerSP" sheetId="9" r:id="rId4"/>
-    <sheet name="2prod" sheetId="19" r:id="rId5"/>
+    <sheet name="farmerSP (2)" sheetId="20" r:id="rId2"/>
+    <sheet name="farmerSP" sheetId="9" r:id="rId3"/>
+    <sheet name="2prod" sheetId="19" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">farmer0!$K$2:$S$2</definedName>
-    <definedName name="solver_adj" localSheetId="3" hidden="1">farmerSP!$K$5:$AE$5</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">'farmerSP (2)'!$K$5:$AQ$5</definedName>
-    <definedName name="solver_adj" localSheetId="1" hidden="1">'farmerSP (3)'!$I$5:$AC$5</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">farmerSP!$K$5:$AE$5</definedName>
+    <definedName name="solver_adj" localSheetId="1" hidden="1">'farmerSP (2)'!$K$5:$AQ$5</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">farmer0!$T$4</definedName>
-    <definedName name="solver_lhs1" localSheetId="3" hidden="1">farmerSP!$AF$7</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$7</definedName>
-    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">farmerSP!$AF$7</definedName>
+    <definedName name="solver_lhs1" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$7</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">farmer0!$T$5:$T$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="3" hidden="1">farmerSP!$AF$8:$AF$19</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$8:$AR$27</definedName>
-    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$8:$AD$19</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">farmerSP!$AF$8:$AF$19</definedName>
+    <definedName name="solver_lhs2" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$8:$AR$27</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">farmer0!$T$5:$T$8</definedName>
-    <definedName name="solver_lhs3" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs3" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_lhs4" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs4" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_lhs4" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs4" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_lhs5" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_lhs5" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_lhs5" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_lhs5" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_num" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="4" hidden="1">'2prod'!$O$10</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'2prod'!$O$10</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">farmer0!$T$3</definedName>
-    <definedName name="solver_opt" localSheetId="3" hidden="1">farmerSP!$AF$6</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">'farmerSP (2)'!$AR$6</definedName>
-    <definedName name="solver_opt" localSheetId="1" hidden="1">'farmerSP (3)'!$AD$6</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">farmerSP!$AF$6</definedName>
+    <definedName name="solver_opt" localSheetId="1" hidden="1">'farmerSP (2)'!$AR$6</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel3" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rel4" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rel4" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rel4" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rel5" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">farmer0!$V$4</definedName>
-    <definedName name="solver_rhs1" localSheetId="3" hidden="1">farmerSP!$AH$7</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">'farmerSP (2)'!$AT$7</definedName>
-    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'farmerSP (3)'!$AF$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">farmerSP!$AH$7</definedName>
+    <definedName name="solver_rhs1" localSheetId="1" hidden="1">'farmerSP (2)'!$AT$7</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">farmer0!$V$5:$V$8</definedName>
-    <definedName name="solver_rhs2" localSheetId="3" hidden="1">farmerSP!$AH$8:$AH$19</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">'farmerSP (2)'!$AT$8:$AT$27</definedName>
-    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'farmerSP (3)'!$AF$8:$AF$19</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">farmerSP!$AH$8:$AH$19</definedName>
+    <definedName name="solver_rhs2" localSheetId="1" hidden="1">'farmerSP (2)'!$AT$8:$AT$27</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">farmer0!$V$5:$V$8</definedName>
-    <definedName name="solver_rhs3" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs3" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_rhs4" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs4" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_rhs4" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs4" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">farmer0!#REF!</definedName>
-    <definedName name="solver_rhs5" localSheetId="3" hidden="1">farmerSP!#REF!</definedName>
-    <definedName name="solver_rhs5" localSheetId="2" hidden="1">'farmerSP (2)'!#REF!</definedName>
-    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'farmerSP (3)'!#REF!</definedName>
+    <definedName name="solver_rhs5" localSheetId="2" hidden="1">farmerSP!#REF!</definedName>
+    <definedName name="solver_rhs5" localSheetId="1" hidden="1">'farmerSP (2)'!#REF!</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="4" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
-    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
   </definedNames>
@@ -210,12 +167,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="74">
   <si>
     <t>=</t>
   </si>
@@ -445,8 +405,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -475,7 +435,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -503,12 +463,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -697,10 +651,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -708,7 +662,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -737,7 +691,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -751,6 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -763,12 +718,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1493,1226 +1442,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56BFB45-A76E-4970-AED8-74E019095023}">
-  <dimension ref="A1:AF19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="11" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="44"/>
-      <c r="H1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1">
-        <v>150</v>
-      </c>
-      <c r="J1">
-        <v>230</v>
-      </c>
-      <c r="K1">
-        <v>260</v>
-      </c>
-      <c r="L1">
-        <v>238</v>
-      </c>
-      <c r="M1">
-        <v>210</v>
-      </c>
-      <c r="N1">
-        <v>-170</v>
-      </c>
-      <c r="O1">
-        <v>-150</v>
-      </c>
-      <c r="P1">
-        <v>-36</v>
-      </c>
-      <c r="Q1">
-        <v>-10</v>
-      </c>
-      <c r="R1">
-        <v>238</v>
-      </c>
-      <c r="S1">
-        <v>210</v>
-      </c>
-      <c r="T1">
-        <v>-170</v>
-      </c>
-      <c r="U1">
-        <v>-150</v>
-      </c>
-      <c r="V1">
-        <v>-36</v>
-      </c>
-      <c r="W1">
-        <v>-10</v>
-      </c>
-      <c r="X1">
-        <v>238</v>
-      </c>
-      <c r="Y1">
-        <v>210</v>
-      </c>
-      <c r="Z1">
-        <v>-170</v>
-      </c>
-      <c r="AA1">
-        <v>-150</v>
-      </c>
-      <c r="AB1">
-        <v>-36</v>
-      </c>
-      <c r="AC1">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2.5</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2">
-        <v>20</v>
-      </c>
-      <c r="F2" s="44"/>
-      <c r="H2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <f>1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="M2">
-        <f t="shared" ref="M2:AC2" si="0">1/3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="O2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="P2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="Q2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="R2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="S2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="T2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="U2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="V2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="W2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="X2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="Y2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="Z2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AA2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AB2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AC2">
-        <f t="shared" si="0"/>
-        <v>0.33333333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>150</v>
-      </c>
-      <c r="C3">
-        <v>230</v>
-      </c>
-      <c r="D3">
-        <v>260</v>
-      </c>
-      <c r="F3" s="44"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4">
-        <v>200</v>
-      </c>
-      <c r="C4">
-        <v>240</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="44"/>
-      <c r="I4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="V4" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="W4" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="X4" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y4" s="46" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z4" s="46" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB4" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC4" s="46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>238</v>
-      </c>
-      <c r="C5">
-        <v>210</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="44"/>
-      <c r="H5" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="27">
-        <v>10</v>
-      </c>
-      <c r="J5" s="27">
-        <v>10</v>
-      </c>
-      <c r="K5" s="27">
-        <v>10</v>
-      </c>
-      <c r="L5" s="27">
-        <v>10</v>
-      </c>
-      <c r="M5" s="27">
-        <v>10</v>
-      </c>
-      <c r="N5" s="27">
-        <v>10</v>
-      </c>
-      <c r="O5" s="27">
-        <v>10</v>
-      </c>
-      <c r="P5" s="27">
-        <v>10</v>
-      </c>
-      <c r="Q5" s="27">
-        <v>10</v>
-      </c>
-      <c r="R5" s="27">
-        <v>10</v>
-      </c>
-      <c r="S5" s="27">
-        <v>10</v>
-      </c>
-      <c r="T5" s="27">
-        <v>10</v>
-      </c>
-      <c r="U5" s="27">
-        <v>10</v>
-      </c>
-      <c r="V5" s="27">
-        <v>10</v>
-      </c>
-      <c r="W5" s="27">
-        <v>10</v>
-      </c>
-      <c r="X5" s="47">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="47">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="47">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="47">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="47">
-        <v>10</v>
-      </c>
-      <c r="AC5" s="47">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="44"/>
-      <c r="H6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="8">
-        <f>I1*I2</f>
-        <v>150</v>
-      </c>
-      <c r="J6" s="9">
-        <f t="shared" ref="J6:AC6" si="1">J1*J2</f>
-        <v>230</v>
-      </c>
-      <c r="K6" s="9">
-        <f t="shared" si="1"/>
-        <v>260</v>
-      </c>
-      <c r="L6" s="8">
-        <f>L1*L2</f>
-        <v>79.333333333333329</v>
-      </c>
-      <c r="M6" s="9">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="N6" s="9">
-        <f t="shared" si="1"/>
-        <v>-56.666666666666664</v>
-      </c>
-      <c r="O6" s="9">
-        <f t="shared" si="1"/>
-        <v>-50</v>
-      </c>
-      <c r="P6" s="9">
-        <f t="shared" si="1"/>
-        <v>-12</v>
-      </c>
-      <c r="Q6" s="10">
-        <f t="shared" si="1"/>
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="R6" s="8">
-        <f t="shared" si="1"/>
-        <v>79.333333333333329</v>
-      </c>
-      <c r="S6" s="9">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="T6" s="9">
-        <f t="shared" si="1"/>
-        <v>-56.666666666666664</v>
-      </c>
-      <c r="U6" s="9">
-        <f t="shared" si="1"/>
-        <v>-50</v>
-      </c>
-      <c r="V6" s="9">
-        <f t="shared" si="1"/>
-        <v>-12</v>
-      </c>
-      <c r="W6" s="10">
-        <f t="shared" si="1"/>
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="X6" s="19">
-        <f t="shared" si="1"/>
-        <v>79.333333333333329</v>
-      </c>
-      <c r="Y6" s="19">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="Z6" s="19">
-        <f t="shared" si="1"/>
-        <v>-56.666666666666664</v>
-      </c>
-      <c r="AA6" s="19">
-        <f t="shared" si="1"/>
-        <v>-50</v>
-      </c>
-      <c r="AB6" s="19">
-        <f t="shared" si="1"/>
-        <v>-12</v>
-      </c>
-      <c r="AC6" s="19">
-        <f t="shared" si="1"/>
-        <v>-3.333333333333333</v>
-      </c>
-      <c r="AD6" s="30">
-        <f>SUMPRODUCT(I6:AC6,$I$5:$AC$5)</f>
-        <v>7220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>170</v>
-      </c>
-      <c r="C7">
-        <v>150</v>
-      </c>
-      <c r="D7">
-        <v>36</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7" s="44"/>
-      <c r="H7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="6"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="6"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="35">
-        <f>SUMPRODUCT(I7:AC7,$I$5:$AC$5)</f>
-        <v>30</v>
-      </c>
-      <c r="AE7" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="31">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
-        <f>B2*B7-B3</f>
-        <v>275</v>
-      </c>
-      <c r="C8">
-        <f>C2*C7-C3</f>
-        <v>220</v>
-      </c>
-      <c r="D8">
-        <f>D2*D7-D3</f>
-        <v>460</v>
-      </c>
-      <c r="E8">
-        <f>D2*E7-D3</f>
-        <v>-60</v>
-      </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8" s="8">
-        <f>1.2*2.5</f>
-        <v>3</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="8">
-        <v>1</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>-1</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="8"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="9"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
-      <c r="AB8" s="9"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="35">
-        <f>SUMPRODUCT(I8:AC8,$I$5:$AC$5)</f>
-        <v>30</v>
-      </c>
-      <c r="AE8" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF8" s="32">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="41"/>
-      <c r="H9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <f>1.2*3</f>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="K9" s="12">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>-1</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>0</v>
-      </c>
-      <c r="R9" s="11"/>
-      <c r="S9" s="4"/>
-      <c r="W9" s="12"/>
-      <c r="X9" s="11"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="35">
-        <f>SUMPRODUCT(I9:AC9,$I$5:$AC$5)</f>
-        <v>36</v>
-      </c>
-      <c r="AE9" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF9" s="33">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F10" s="44"/>
-      <c r="G10" s="41"/>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="11">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="12">
-        <f>1.2*20</f>
-        <v>24</v>
-      </c>
-      <c r="L10" s="11">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-1</v>
-      </c>
-      <c r="Q10" s="12">
-        <v>-1</v>
-      </c>
-      <c r="R10" s="11"/>
-      <c r="S10" s="4"/>
-      <c r="W10" s="12"/>
-      <c r="X10" s="11"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="35">
-        <f>SUMPRODUCT(I10:AC10,$I$5:$AC$5)</f>
-        <v>220</v>
-      </c>
-      <c r="AE10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF10" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F11" s="44"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0</v>
-      </c>
-      <c r="K11" s="15">
-        <v>0</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="14">
-        <v>0</v>
-      </c>
-      <c r="N11" s="14">
-        <v>0</v>
-      </c>
-      <c r="O11" s="14">
-        <v>0</v>
-      </c>
-      <c r="P11" s="14">
-        <v>-1</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>0</v>
-      </c>
-      <c r="R11" s="13"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="35">
-        <f>SUMPRODUCT(I11:AC11,$I$5:$AC$5)</f>
-        <v>-10</v>
-      </c>
-      <c r="AE11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF11" s="33">
-        <v>-6000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F12" s="44"/>
-      <c r="G12" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="8">
-        <v>1</v>
-      </c>
-      <c r="S12" s="9">
-        <v>0</v>
-      </c>
-      <c r="T12" s="9">
-        <v>-1</v>
-      </c>
-      <c r="U12" s="9">
-        <v>0</v>
-      </c>
-      <c r="V12" s="9">
-        <v>0</v>
-      </c>
-      <c r="W12" s="10">
-        <v>0</v>
-      </c>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="35">
-        <f>SUMPRODUCT(I12:AC12,$I$5:$AC$5)</f>
-        <v>25</v>
-      </c>
-      <c r="AE12" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF12" s="31">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F13" s="44"/>
-      <c r="G13" s="41"/>
-      <c r="H13" t="s">
-        <v>3</v>
-      </c>
-      <c r="I13" s="11">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>3</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0</v>
-      </c>
-      <c r="L13" s="11"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="11">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>1</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>-1</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13" s="12">
-        <v>0</v>
-      </c>
-      <c r="X13" s="11"/>
-      <c r="AC13" s="12"/>
-      <c r="AD13" s="35">
-        <f>SUMPRODUCT(I13:AC13,$I$5:$AC$5)</f>
-        <v>30</v>
-      </c>
-      <c r="AE13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF13" s="33">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F14" s="44"/>
-      <c r="G14" s="41"/>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="12">
-        <v>20</v>
-      </c>
-      <c r="L14" s="11"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="11">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>-1</v>
-      </c>
-      <c r="W14" s="12">
-        <v>-1</v>
-      </c>
-      <c r="X14" s="11"/>
-      <c r="AC14" s="12"/>
-      <c r="AD14" s="35">
-        <f>SUMPRODUCT(I14:AC14,$I$5:$AC$5)</f>
-        <v>180</v>
-      </c>
-      <c r="AE14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF14" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F15" s="44"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0</v>
-      </c>
-      <c r="J15" s="14">
-        <v>0</v>
-      </c>
-      <c r="K15" s="15">
-        <v>0</v>
-      </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="13">
-        <v>0</v>
-      </c>
-      <c r="S15" s="14">
-        <v>0</v>
-      </c>
-      <c r="T15" s="14">
-        <v>0</v>
-      </c>
-      <c r="U15" s="14">
-        <v>0</v>
-      </c>
-      <c r="V15" s="14">
-        <v>-1</v>
-      </c>
-      <c r="W15" s="15">
-        <v>0</v>
-      </c>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="15"/>
-      <c r="AD15" s="35">
-        <f>SUMPRODUCT(I15:AC15,$I$5:$AC$5)</f>
-        <v>-10</v>
-      </c>
-      <c r="AE15" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF15" s="34">
-        <v>-6000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="F16" s="44"/>
-      <c r="G16" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="8">
-        <f>0.8*2.5</f>
-        <v>2</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10">
-        <v>0</v>
-      </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="8">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="9">
-        <v>-1</v>
-      </c>
-      <c r="AA16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="35">
-        <f>SUMPRODUCT(I16:AC16,$I$5:$AC$5)</f>
-        <v>20</v>
-      </c>
-      <c r="AE16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF16" s="33">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="6:32" x14ac:dyDescent="0.25">
-      <c r="F17" s="44"/>
-      <c r="G17" s="41"/>
-      <c r="H17" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="11">
-        <v>0</v>
-      </c>
-      <c r="J17" s="45">
-        <f>0.8*3</f>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="K17" s="12">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="11"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>1</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>-1</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="35">
-        <f>SUMPRODUCT(I17:AC17,$I$5:$AC$5)</f>
-        <v>24</v>
-      </c>
-      <c r="AE17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF17" s="33">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="18" spans="6:32" x14ac:dyDescent="0.25">
-      <c r="F18" s="44"/>
-      <c r="G18" s="41"/>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="11">
-        <v>0</v>
-      </c>
-      <c r="J18" s="45">
-        <v>0</v>
-      </c>
-      <c r="K18" s="12">
-        <f>0.8*20</f>
-        <v>16</v>
-      </c>
-      <c r="L18" s="11"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="11"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y18">
-        <v>0</v>
-      </c>
-      <c r="Z18">
-        <v>0</v>
-      </c>
-      <c r="AA18">
-        <v>0</v>
-      </c>
-      <c r="AB18">
-        <v>-1</v>
-      </c>
-      <c r="AC18" s="12">
-        <v>-1</v>
-      </c>
-      <c r="AD18" s="35">
-        <f>SUMPRODUCT(I18:AC18,$I$5:$AC$5)</f>
-        <v>140</v>
-      </c>
-      <c r="AE18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF18" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="6:32" x14ac:dyDescent="0.25">
-      <c r="F19" s="44"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="13">
-        <v>0</v>
-      </c>
-      <c r="J19" s="14">
-        <v>0</v>
-      </c>
-      <c r="K19" s="15">
-        <v>0</v>
-      </c>
-      <c r="L19" s="13"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="15"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="13">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="14">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="14">
-        <v>-1</v>
-      </c>
-      <c r="AC19" s="15">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="35">
-        <f>SUMPRODUCT(I19:AC19,$I$5:$AC$5)</f>
-        <v>-10</v>
-      </c>
-      <c r="AE19" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF19" s="34">
-        <v>-6000</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="G12:G15"/>
-    <mergeCell ref="G16:G19"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25CF1EED-2747-49F4-88EF-A266F263C174}">
   <dimension ref="A1:AT27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2723,27 +1452,30 @@
     <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="3.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="4.42578125" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="6" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="6" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="7.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:46" x14ac:dyDescent="0.25">
@@ -3360,7 +2092,7 @@
         <f t="shared" si="0"/>
         <v>-0.5</v>
       </c>
-      <c r="AR6" s="30">
+      <c r="AR6" s="40">
         <f t="shared" ref="AR6:AR27" si="1">SUMPRODUCT(K6:AQ6,$K$5:$AQ$5)</f>
         <v>-77058.000000000015</v>
       </c>
@@ -3454,7 +2186,7 @@
         <f>D2*E7-D3</f>
         <v>-60</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="41" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -3539,7 +2271,7 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="41"/>
+      <c r="I9" s="42"/>
       <c r="J9" t="s">
         <v>3</v>
       </c>
@@ -3592,7 +2324,7 @@
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I10" s="41"/>
+      <c r="I10" s="42"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
@@ -3645,7 +2377,7 @@
       </c>
     </row>
     <row r="11" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I11" s="42"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
       </c>
@@ -3712,7 +2444,7 @@
       </c>
     </row>
     <row r="12" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="44" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -3781,7 +2513,7 @@
       </c>
     </row>
     <row r="13" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I13" s="41"/>
+      <c r="I13" s="42"/>
       <c r="J13" t="s">
         <v>3</v>
       </c>
@@ -3832,7 +2564,7 @@
       </c>
     </row>
     <row r="14" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I14" s="41"/>
+      <c r="I14" s="42"/>
       <c r="J14" t="s">
         <v>27</v>
       </c>
@@ -3883,7 +2615,7 @@
       </c>
     </row>
     <row r="15" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I15" s="42"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
       </c>
@@ -3950,7 +2682,7 @@
       </c>
     </row>
     <row r="16" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="I16" s="43" t="s">
+      <c r="I16" s="44" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -4020,7 +2752,7 @@
       </c>
     </row>
     <row r="17" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" t="s">
         <v>3</v>
       </c>
@@ -4072,7 +2804,7 @@
       </c>
     </row>
     <row r="18" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I18" s="41"/>
+      <c r="I18" s="42"/>
       <c r="J18" t="s">
         <v>27</v>
       </c>
@@ -4124,7 +2856,7 @@
       </c>
     </row>
     <row r="19" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I19" s="42"/>
+      <c r="I19" s="43"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
       </c>
@@ -4188,7 +2920,7 @@
       </c>
     </row>
     <row r="20" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I20" s="43"/>
+      <c r="I20" s="44"/>
       <c r="J20" s="9" t="s">
         <v>2</v>
       </c>
@@ -4255,7 +2987,7 @@
       </c>
     </row>
     <row r="21" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I21" s="41"/>
+      <c r="I21" s="42"/>
       <c r="J21" t="s">
         <v>3</v>
       </c>
@@ -4306,7 +3038,7 @@
       </c>
     </row>
     <row r="22" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I22" s="41"/>
+      <c r="I22" s="42"/>
       <c r="J22" t="s">
         <v>27</v>
       </c>
@@ -4357,7 +3089,7 @@
       </c>
     </row>
     <row r="23" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I23" s="42"/>
+      <c r="I23" s="43"/>
       <c r="J23" s="14" t="s">
         <v>28</v>
       </c>
@@ -4421,7 +3153,7 @@
       </c>
     </row>
     <row r="24" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I24" s="43"/>
+      <c r="I24" s="44"/>
       <c r="J24" s="9" t="s">
         <v>2</v>
       </c>
@@ -4488,7 +3220,7 @@
       </c>
     </row>
     <row r="25" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I25" s="41"/>
+      <c r="I25" s="42"/>
       <c r="J25" t="s">
         <v>3</v>
       </c>
@@ -4539,7 +3271,7 @@
       </c>
     </row>
     <row r="26" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I26" s="41"/>
+      <c r="I26" s="42"/>
       <c r="J26" t="s">
         <v>27</v>
       </c>
@@ -4590,7 +3322,7 @@
       </c>
     </row>
     <row r="27" spans="9:46" x14ac:dyDescent="0.25">
-      <c r="I27" s="42"/>
+      <c r="I27" s="43"/>
       <c r="J27" s="14" t="s">
         <v>28</v>
       </c>
@@ -4666,7 +3398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D37E63B8-EB9D-4227-BEBC-562734DDEEDE}">
   <dimension ref="A1:AH19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5204,7 +3936,7 @@
         <f>D2*E7-D3</f>
         <v>-60</v>
       </c>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="41" t="s">
         <v>53</v>
       </c>
       <c r="J8" s="9" t="s">
@@ -5277,7 +4009,7 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="41"/>
+      <c r="I9" s="42"/>
       <c r="J9" t="s">
         <v>3</v>
       </c>
@@ -5326,7 +4058,7 @@
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I10" s="41"/>
+      <c r="I10" s="42"/>
       <c r="J10" t="s">
         <v>27</v>
       </c>
@@ -5375,7 +4107,7 @@
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I11" s="42"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="14" t="s">
         <v>28</v>
       </c>
@@ -5430,7 +4162,7 @@
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I12" s="43" t="s">
+      <c r="I12" s="44" t="s">
         <v>49</v>
       </c>
       <c r="J12" s="9" t="s">
@@ -5487,7 +4219,7 @@
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I13" s="41"/>
+      <c r="I13" s="42"/>
       <c r="J13" t="s">
         <v>3</v>
       </c>
@@ -5534,7 +4266,7 @@
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I14" s="41"/>
+      <c r="I14" s="42"/>
       <c r="J14" t="s">
         <v>27</v>
       </c>
@@ -5581,7 +4313,7 @@
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I15" s="42"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="14" t="s">
         <v>28</v>
       </c>
@@ -5636,7 +4368,7 @@
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="I16" s="43" t="s">
+      <c r="I16" s="44" t="s">
         <v>52</v>
       </c>
       <c r="J16" s="9" t="s">
@@ -5694,7 +4426,7 @@
       </c>
     </row>
     <row r="17" spans="9:34" x14ac:dyDescent="0.25">
-      <c r="I17" s="41"/>
+      <c r="I17" s="42"/>
       <c r="J17" t="s">
         <v>3</v>
       </c>
@@ -5742,7 +4474,7 @@
       </c>
     </row>
     <row r="18" spans="9:34" x14ac:dyDescent="0.25">
-      <c r="I18" s="41"/>
+      <c r="I18" s="42"/>
       <c r="J18" t="s">
         <v>27</v>
       </c>
@@ -5790,7 +4522,7 @@
       </c>
     </row>
     <row r="19" spans="9:34" x14ac:dyDescent="0.25">
-      <c r="I19" s="42"/>
+      <c r="I19" s="43"/>
       <c r="J19" s="14" t="s">
         <v>28</v>
       </c>
@@ -5854,7 +4586,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E936C5E6-48EB-470A-826D-E40B341C7C76}">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
